--- a/outputs/report/fly_tipping_story_data.xlsx
+++ b/outputs/report/fly_tipping_story_data.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">One sheet per chart in the report (docs/story.md). Derived columns (percentage changes, indexes, rates, totals) are formulas. A rate ratio of 1.20 means 20% more fly-tipping per resident.</t>
   </si>
   <si>
-    <t xml:space="preserve">The map of drive-time changes (figure 2) is in drive_time_change_lsoa.parquet and recycling_centres.parquet (GeoParquet, British National Grid; centres for England only, as on the map), which open in QGIS, ArcGIS, R (sf) or Python (geopandas).</t>
+    <t xml:space="preserve">The map of drive-time changes (figure 2) is in drive_time_change_lsoa.parquet and recycling_centres.parquet (GeoParquet, British National Grid; centres for England only, as on the map), which open in QGIS, ArcGIS, R (sf) or Python (geopandas). lsoa_population_weighted_centroids.parquet has the point drive times are measured from for every neighbourhood.</t>
   </si>
   <si>
     <t xml:space="preserve">Sources: Defra and Welsh Government fly-tipping statistics; FixMyStreet (mySociety); ONS Census 2011 and 2021, population estimates and consumer prices index; council revenue outturn (MHCLG); Environment Agency and Natural Resources Wales site records. Open Government Licence v3.0. Code: github.com/kochal/litter.</t>
